--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="128">
   <si>
     <t>Categoría</t>
   </si>
@@ -76,12 +76,18 @@
     <t>2252-1D</t>
   </si>
   <si>
+    <t>3202C9129</t>
+  </si>
+  <si>
     <t>363-4009/1613</t>
   </si>
   <si>
     <t>4302712/8398</t>
   </si>
   <si>
+    <t>7215/07</t>
+  </si>
+  <si>
     <t>9501/9471 2TOR</t>
   </si>
   <si>
@@ -118,9 +124,6 @@
     <t>20461B/5903</t>
   </si>
   <si>
-    <t>4301843/6894</t>
-  </si>
-  <si>
     <t>B39882-1</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
     <t>R002305</t>
   </si>
   <si>
+    <t>R802689/R802447</t>
+  </si>
+  <si>
     <t>4302670</t>
   </si>
   <si>
@@ -172,6 +178,9 @@
     <t>6PK1620GATES/K060637</t>
   </si>
   <si>
+    <t>SAP1024L</t>
+  </si>
+  <si>
     <t>FIRESTONE</t>
   </si>
   <si>
@@ -187,12 +196,12 @@
     <t>GTD</t>
   </si>
   <si>
+    <t>MERITOR</t>
+  </si>
+  <si>
     <t>STEMCO</t>
   </si>
   <si>
-    <t>MERITOR</t>
-  </si>
-  <si>
     <t>MAHLE</t>
   </si>
   <si>
@@ -229,6 +238,9 @@
     <t>GATES</t>
   </si>
   <si>
+    <t>SAP</t>
+  </si>
+  <si>
     <t>BOLSA SILLA CZ TODAS INTER</t>
   </si>
   <si>
@@ -247,12 +259,18 @@
     <t>VALVULA NIVELADORA TANQUE COMBUSTIBLE</t>
   </si>
   <si>
+    <t>EJE LATERAL TRAS 46160 ANTIPATINAJE RECT</t>
+  </si>
+  <si>
     <t>TAPA NEGRA DEFENDER  PASTA 5 1/2" GRANDE</t>
   </si>
   <si>
     <t>RODILLO TREN FIJO PARTE TRAS - TODAS 18</t>
   </si>
   <si>
+    <t>BOLSA SUSPENSION CABINA FREIGTHLINER</t>
+  </si>
+  <si>
     <t>BOLSA TAN10.12ANx5.87CCx24.50AL+7.88D+2T</t>
   </si>
   <si>
@@ -289,9 +307,6 @@
     <t>PIÑÓN 4TA TREN FIJO 14715/16915</t>
   </si>
   <si>
-    <t>ARANDELA TORNILLO PUNTA EJE MONO 918</t>
-  </si>
-  <si>
     <t>CORONA Y SPEED DP 9X41</t>
   </si>
   <si>
@@ -307,6 +322,9 @@
     <t>TUERCA 1227R-330</t>
   </si>
   <si>
+    <t>RACHE AUTO SH CC 5 1/2" TP2 1-1/2"28E</t>
+  </si>
+  <si>
     <t>PIÑON 2DA CORREDIZO FO-16E318B-MXP</t>
   </si>
   <si>
@@ -343,9 +361,15 @@
     <t>CORREA AIRE ACONDICIONADO ACANALADA P/ALTERN . EAGLE Y PROSTAR INTERNATIONAL PAYSTAR MOD.08-12, A.A. INTERNATIONAL PROSTAR MOTOR CUMMINS ISX MOD.2014 6 CANALES</t>
   </si>
   <si>
+    <t>CÁMARA DE FRENO DE SERVICIO TIPO 24 CON CONJUNTO DE HORQUILLA</t>
+  </si>
+  <si>
     <t>CVG</t>
   </si>
   <si>
+    <t>USA</t>
+  </si>
+  <si>
     <t>WAP/TRANSMISION</t>
   </si>
   <si>
@@ -367,13 +391,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/09/2025 09:57:11</t>
+    <t>Período: 31/10/2025 09:15:37</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 08/09/2025 09:57:34</t>
+    <t>Fecha y hora de generación: 21/10/2025 09:16:04</t>
   </si>
 </sst>
 </file>
@@ -787,28 +811,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -824,7 +848,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -840,12 +864,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -897,19 +921,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I10" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -929,19 +953,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I11" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -961,19 +985,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -993,19 +1017,19 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1025,19 +1049,19 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1057,19 +1081,19 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I15" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -1089,28 +1113,28 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I16" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K16">
-        <v>41542.9</v>
+        <v>525495.8</v>
       </c>
       <c r="L16">
-        <v>83085.8</v>
+        <v>6305949.6</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1121,28 +1145,28 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>52431.62</v>
+        <v>41542.9</v>
       </c>
       <c r="L17">
-        <v>209726.48</v>
+        <v>83085.8</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1153,28 +1177,28 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I18" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>558922.2</v>
+        <v>52431.62</v>
       </c>
       <c r="L18">
-        <v>558922.2</v>
+        <v>209726.48</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1185,28 +1209,28 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I19" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J19">
         <v>2</v>
       </c>
       <c r="K19">
-        <v>109890.41</v>
+        <v>91384.38</v>
       </c>
       <c r="L19">
-        <v>219780.82</v>
+        <v>182768.76</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1217,28 +1241,28 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I20" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
-        <v>237833.89</v>
+        <v>558922.2</v>
       </c>
       <c r="L20">
-        <v>237833.89</v>
+        <v>558922.2</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1249,28 +1273,28 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I21" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J21">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K21">
-        <v>297747.47</v>
+        <v>109890.41</v>
       </c>
       <c r="L21">
-        <v>5954949.4</v>
+        <v>219780.82</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1281,28 +1305,28 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I22" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>94848.23</v>
+        <v>237833.89</v>
       </c>
       <c r="L22">
-        <v>189696.46</v>
+        <v>237833.89</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1313,28 +1337,28 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I23" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K23">
-        <v>348949.42</v>
+        <v>297747.47</v>
       </c>
       <c r="L23">
-        <v>348949.42</v>
+        <v>5954949.4</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1345,28 +1369,28 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I24" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24">
-        <v>150117.48</v>
+        <v>94848.23</v>
       </c>
       <c r="L24">
-        <v>150117.48</v>
+        <v>189696.46</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1377,28 +1401,28 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I25" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>3641.01</v>
+        <v>348949.42</v>
       </c>
       <c r="L25">
-        <v>18205.05</v>
+        <v>348949.42</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1409,28 +1433,28 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I26" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>20800.67</v>
+        <v>150117.48</v>
       </c>
       <c r="L26">
-        <v>41601.34</v>
+        <v>150117.48</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1441,28 +1465,28 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I27" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J27">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>3836.09</v>
+        <v>3641.01</v>
       </c>
       <c r="L27">
-        <v>141935.33</v>
+        <v>18205.05</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1473,28 +1497,28 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I28" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J28">
         <v>2</v>
       </c>
       <c r="K28">
-        <v>344212.26</v>
+        <v>20800.67</v>
       </c>
       <c r="L28">
-        <v>688424.52</v>
+        <v>41601.34</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1505,28 +1529,28 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I29" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="K29">
-        <v>206249.01</v>
+        <v>3936.75</v>
       </c>
       <c r="L29">
-        <v>206249.01</v>
+        <v>185027.25</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1537,28 +1561,28 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I30" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30">
-        <v>41896.42</v>
+        <v>312918.09</v>
       </c>
       <c r="L30">
-        <v>83792.84</v>
+        <v>938754.27</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1569,28 +1593,28 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I31" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="K31">
-        <v>2444357.96</v>
+        <v>206249.01</v>
       </c>
       <c r="L31">
-        <v>2444357.96</v>
+        <v>206249.01</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1601,28 +1625,28 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F32" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I32" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32">
-        <v>216538.69</v>
+        <v>2444357.96</v>
       </c>
       <c r="L32">
-        <v>216538.69</v>
+        <v>2444357.96</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1633,92 +1657,92 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="I33" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <v>286676.26</v>
+        <v>216538.69</v>
       </c>
       <c r="L33">
-        <v>286676.26</v>
+        <v>216538.69</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F34" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I34" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J34">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="K34">
-        <v>18302.68</v>
+        <v>286676.26</v>
       </c>
       <c r="L34">
-        <v>3660536</v>
+        <v>286676.26</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E35" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I35" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J35">
-        <v>60</v>
+        <v>786</v>
       </c>
       <c r="K35">
-        <v>20614.17</v>
+        <v>18048.24</v>
       </c>
       <c r="L35">
-        <v>1236850.2</v>
+        <v>14185916.64</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1729,28 +1753,28 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I36" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K36">
-        <v>261801.89</v>
+        <v>20614.17</v>
       </c>
       <c r="L36">
-        <v>261801.89</v>
+        <v>1236850.2</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1761,28 +1785,28 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I37" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K37">
-        <v>75557.81</v>
+        <v>162426.15</v>
       </c>
       <c r="L37">
-        <v>75557.81</v>
+        <v>2111539.95</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -1793,28 +1817,28 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I38" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J38">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>122009.29</v>
+        <v>261801.89</v>
       </c>
       <c r="L38">
-        <v>2318176.51</v>
+        <v>261801.89</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -1825,60 +1849,60 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I39" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J39">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="K39">
-        <v>3512.14</v>
+        <v>75557.81</v>
       </c>
       <c r="L39">
-        <v>1264370.4</v>
+        <v>75557.81</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J40">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="K40">
-        <v>12659.05</v>
+        <v>122009.29</v>
       </c>
       <c r="L40">
-        <v>4607894.2</v>
+        <v>2318176.51</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1889,60 +1913,60 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I41" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J41">
-        <v>8</v>
+        <v>360</v>
       </c>
       <c r="K41">
-        <v>229850.62</v>
+        <v>3512.14</v>
       </c>
       <c r="L41">
-        <v>1838804.96</v>
+        <v>1264370.4</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E42" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I42" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J42">
-        <v>60</v>
+        <v>364</v>
       </c>
       <c r="K42">
-        <v>663.89</v>
+        <v>12659.05</v>
       </c>
       <c r="L42">
-        <v>39833.4</v>
+        <v>4607894.2</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -1953,28 +1977,28 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D43" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F43" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="I43" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K43">
-        <v>209975.56</v>
+        <v>229850.62</v>
       </c>
       <c r="L43">
-        <v>209975.56</v>
+        <v>1838804.96</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -1985,28 +2009,28 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E44" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F44" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="I44" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K44">
-        <v>163002.7</v>
+        <v>663.89</v>
       </c>
       <c r="L44">
-        <v>163002.7</v>
+        <v>39833.4</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2017,28 +2041,28 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I45" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="K45">
-        <v>15384.67</v>
+        <v>209975.56</v>
       </c>
       <c r="L45">
-        <v>15384.67</v>
+        <v>209975.56</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2049,28 +2073,28 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F46" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="I46" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K46">
-        <v>193066.84</v>
+        <v>163002.7</v>
       </c>
       <c r="L46">
-        <v>386133.68</v>
+        <v>163002.7</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2081,28 +2105,124 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D47" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I47" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>15384.67</v>
+      </c>
+      <c r="L47">
+        <v>15384.67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" t="s">
+        <v>113</v>
+      </c>
+      <c r="E48" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48" t="s">
+        <v>73</v>
+      </c>
+      <c r="I48" t="s">
+        <v>119</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48">
+        <v>193066.84</v>
+      </c>
+      <c r="L48">
+        <v>386133.68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49" t="s">
+        <v>73</v>
+      </c>
+      <c r="F49" t="s">
+        <v>73</v>
+      </c>
+      <c r="I49" t="s">
+        <v>119</v>
+      </c>
+      <c r="J49">
         <v>5</v>
       </c>
-      <c r="K47">
+      <c r="K49">
         <v>26517.61</v>
       </c>
-      <c r="L47">
+      <c r="L49">
         <v>132588.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E50" t="s">
+        <v>117</v>
+      </c>
+      <c r="F50" t="s">
+        <v>117</v>
+      </c>
+      <c r="I50" t="s">
+        <v>119</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>39099.54</v>
+      </c>
+      <c r="L50">
+        <v>39099.54</v>
       </c>
     </row>
   </sheetData>

--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -391,13 +391,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 09:44:16</t>
+    <t>Período: 31/10/2025 12:37:31</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 23/10/2025 09:52:47</t>
+    <t>Fecha y hora de generación: 27/10/2025 12:37:55</t>
   </si>
 </sst>
 </file>
@@ -1736,13 +1736,13 @@
         <v>119</v>
       </c>
       <c r="J35">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="K35">
         <v>18048.24</v>
       </c>
       <c r="L35">
-        <v>14185916.64</v>
+        <v>14294206.08</v>
       </c>
     </row>
     <row r="36" spans="1:12">

--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -70,6 +70,9 @@
     <t>1824680C1</t>
   </si>
   <si>
+    <t>1S5-164/21128983</t>
+  </si>
+  <si>
     <t>20382B</t>
   </si>
   <si>
@@ -163,9 +166,6 @@
     <t>14897</t>
   </si>
   <si>
-    <t>286171R</t>
-  </si>
-  <si>
     <t>4303796/4301527WAP</t>
   </si>
   <si>
@@ -193,6 +193,9 @@
     <t>INTERNATIONAL</t>
   </si>
   <si>
+    <t>GOODYEAR</t>
+  </si>
+  <si>
     <t>GTD</t>
   </si>
   <si>
@@ -226,9 +229,6 @@
     <t>ELGIN</t>
   </si>
   <si>
-    <t>BENDIX</t>
-  </si>
-  <si>
     <t>WAP</t>
   </si>
   <si>
@@ -253,6 +253,9 @@
     <t>ROTOR TODAS LAS VALVULAS DT466 ELECTRONI</t>
   </si>
   <si>
+    <t>BOLSA SUSPENSION CABINA MACK VISION</t>
+  </si>
+  <si>
     <t>PIÑÓN 2DA TREN FIJO 14715/16915</t>
   </si>
   <si>
@@ -346,9 +349,6 @@
     <t>RESORTE</t>
   </si>
   <si>
-    <t>VALVULA DE FRENO E-6 PARA CHEVROLET Y BRIGADIER (REMANUFACTURADA COLOR AZUL)</t>
-  </si>
-  <si>
     <t>PIÑON DE 4TA EJE CORREDIZO 4205</t>
   </si>
   <si>
@@ -391,13 +391,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 12:37:31</t>
+    <t>Período: 31/10/2025 08:45:56</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 27/10/2025 12:37:55</t>
+    <t>Fecha y hora de generación: 30/10/2025 08:46:54</t>
   </si>
 </sst>
 </file>
@@ -1049,28 +1049,28 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I14" t="s">
         <v>119</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>177348.88</v>
+        <v>69586.60000000001</v>
       </c>
       <c r="L14">
-        <v>354697.76</v>
+        <v>347933</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1081,28 +1081,28 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I15" t="s">
         <v>119</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>70851.95</v>
+        <v>177348.88</v>
       </c>
       <c r="L15">
-        <v>283407.8</v>
+        <v>354697.76</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1128,13 +1128,13 @@
         <v>119</v>
       </c>
       <c r="J16">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K16">
-        <v>525495.8</v>
+        <v>70851.95</v>
       </c>
       <c r="L16">
-        <v>6305949.6</v>
+        <v>283407.8</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1160,13 +1160,13 @@
         <v>119</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K17">
-        <v>41542.9</v>
+        <v>525495.8</v>
       </c>
       <c r="L17">
-        <v>83085.8</v>
+        <v>6305949.6</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1177,28 +1177,28 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
         <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I18" t="s">
         <v>119</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>52431.62</v>
+        <v>41542.9</v>
       </c>
       <c r="L18">
-        <v>209726.48</v>
+        <v>83085.8</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1209,28 +1209,28 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
         <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I19" t="s">
         <v>119</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>91384.38</v>
+        <v>52431.62</v>
       </c>
       <c r="L19">
-        <v>182768.76</v>
+        <v>209726.48</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1256,13 +1256,13 @@
         <v>119</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20">
-        <v>558922.2</v>
+        <v>91384.38</v>
       </c>
       <c r="L20">
-        <v>558922.2</v>
+        <v>182768.76</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1273,28 +1273,28 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
         <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I21" t="s">
         <v>119</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>109890.41</v>
+        <v>558922.2</v>
       </c>
       <c r="L21">
-        <v>219780.82</v>
+        <v>558922.2</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1305,28 +1305,28 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
         <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I22" t="s">
         <v>119</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>237833.89</v>
+        <v>109890.41</v>
       </c>
       <c r="L22">
-        <v>237833.89</v>
+        <v>219780.82</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1337,28 +1337,28 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
         <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
         <v>119</v>
       </c>
       <c r="J23">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>297747.47</v>
+        <v>237833.89</v>
       </c>
       <c r="L23">
-        <v>5954949.4</v>
+        <v>237833.89</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1369,28 +1369,28 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
         <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I24" t="s">
         <v>119</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K24">
-        <v>94848.23</v>
+        <v>297747.47</v>
       </c>
       <c r="L24">
-        <v>189696.46</v>
+        <v>5954949.4</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1407,22 +1407,22 @@
         <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I25" t="s">
         <v>119</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25">
-        <v>348949.42</v>
+        <v>94848.23</v>
       </c>
       <c r="L25">
-        <v>348949.42</v>
+        <v>189696.46</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1451,10 +1451,10 @@
         <v>1</v>
       </c>
       <c r="K26">
-        <v>150117.48</v>
+        <v>348949.42</v>
       </c>
       <c r="L26">
-        <v>150117.48</v>
+        <v>348949.42</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1465,28 +1465,28 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
         <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I27" t="s">
         <v>119</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>3641.01</v>
+        <v>150117.48</v>
       </c>
       <c r="L27">
-        <v>18205.05</v>
+        <v>150117.48</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1512,13 +1512,13 @@
         <v>119</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>20800.67</v>
+        <v>3641.01</v>
       </c>
       <c r="L28">
-        <v>41601.34</v>
+        <v>18205.05</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1544,13 +1544,13 @@
         <v>119</v>
       </c>
       <c r="J29">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="K29">
-        <v>3936.75</v>
+        <v>20800.67</v>
       </c>
       <c r="L29">
-        <v>185027.25</v>
+        <v>41601.34</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1561,7 +1561,7 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D30" t="s">
         <v>95</v>
@@ -1570,19 +1570,19 @@
         <v>56</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I30" t="s">
         <v>119</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="K30">
-        <v>312918.09</v>
+        <v>3936.75</v>
       </c>
       <c r="L30">
-        <v>938754.27</v>
+        <v>185027.25</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1593,7 +1593,7 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
         <v>96</v>
@@ -1602,19 +1602,19 @@
         <v>56</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I31" t="s">
         <v>119</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31">
-        <v>206249.01</v>
+        <v>312918.09</v>
       </c>
       <c r="L31">
-        <v>206249.01</v>
+        <v>938754.27</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1625,16 +1625,16 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D32" t="s">
         <v>97</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F32" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I32" t="s">
         <v>119</v>
@@ -1643,10 +1643,10 @@
         <v>1</v>
       </c>
       <c r="K32">
-        <v>2444357.96</v>
+        <v>206249.01</v>
       </c>
       <c r="L32">
-        <v>2444357.96</v>
+        <v>206249.01</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1657,16 +1657,16 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s">
         <v>98</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I33" t="s">
         <v>119</v>
@@ -1675,10 +1675,10 @@
         <v>1</v>
       </c>
       <c r="K33">
-        <v>216538.69</v>
+        <v>2444357.96</v>
       </c>
       <c r="L33">
-        <v>216538.69</v>
+        <v>2444357.96</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1689,16 +1689,16 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
         <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F34" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I34" t="s">
         <v>119</v>
@@ -1707,74 +1707,74 @@
         <v>1</v>
       </c>
       <c r="K34">
-        <v>286676.26</v>
+        <v>216538.69</v>
       </c>
       <c r="L34">
-        <v>286676.26</v>
+        <v>216538.69</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D35" t="s">
         <v>100</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F35" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="I35" t="s">
         <v>119</v>
       </c>
       <c r="J35">
-        <v>792</v>
+        <v>1</v>
       </c>
       <c r="K35">
-        <v>18048.24</v>
+        <v>286676.26</v>
       </c>
       <c r="L35">
-        <v>14294206.08</v>
+        <v>286676.26</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
         <v>101</v>
       </c>
       <c r="E36" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I36" t="s">
         <v>119</v>
       </c>
       <c r="J36">
-        <v>60</v>
+        <v>792</v>
       </c>
       <c r="K36">
-        <v>20614.17</v>
+        <v>18048.24</v>
       </c>
       <c r="L36">
-        <v>1236850.2</v>
+        <v>14294206.08</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1785,28 +1785,28 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D37" t="s">
         <v>102</v>
       </c>
       <c r="E37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" t="s">
+        <v>61</v>
+      </c>
+      <c r="I37" t="s">
+        <v>119</v>
+      </c>
+      <c r="J37">
         <v>60</v>
       </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-      <c r="I37" t="s">
-        <v>119</v>
-      </c>
-      <c r="J37">
-        <v>13</v>
-      </c>
       <c r="K37">
-        <v>162426.15</v>
+        <v>20614.17</v>
       </c>
       <c r="L37">
-        <v>2111539.95</v>
+        <v>1236850.2</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -1817,28 +1817,28 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D38" t="s">
         <v>103</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I38" t="s">
         <v>119</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K38">
-        <v>261801.89</v>
+        <v>162426.15</v>
       </c>
       <c r="L38">
-        <v>261801.89</v>
+        <v>2111539.95</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -1849,16 +1849,16 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D39" t="s">
         <v>104</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F39" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="I39" t="s">
         <v>119</v>
@@ -1867,10 +1867,10 @@
         <v>1</v>
       </c>
       <c r="K39">
-        <v>75557.81</v>
+        <v>261801.89</v>
       </c>
       <c r="L39">
-        <v>75557.81</v>
+        <v>261801.89</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1881,28 +1881,28 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D40" t="s">
         <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F40" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="I40" t="s">
         <v>119</v>
       </c>
       <c r="J40">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K40">
-        <v>122009.29</v>
+        <v>75557.81</v>
       </c>
       <c r="L40">
-        <v>2318176.51</v>
+        <v>75557.81</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1913,92 +1913,92 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D41" t="s">
         <v>106</v>
       </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I41" t="s">
         <v>119</v>
       </c>
       <c r="J41">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="K41">
-        <v>3512.14</v>
+        <v>122009.29</v>
       </c>
       <c r="L41">
-        <v>1264370.4</v>
+        <v>2318176.51</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D42" t="s">
         <v>107</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I42" t="s">
         <v>119</v>
       </c>
       <c r="J42">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="K42">
-        <v>12659.05</v>
+        <v>3512.14</v>
       </c>
       <c r="L42">
-        <v>4607894.2</v>
+        <v>1264370.4</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D43" t="s">
         <v>108</v>
       </c>
       <c r="E43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I43" t="s">
         <v>119</v>
       </c>
       <c r="J43">
-        <v>8</v>
+        <v>364</v>
       </c>
       <c r="K43">
-        <v>229850.62</v>
+        <v>12659.05</v>
       </c>
       <c r="L43">
-        <v>1838804.96</v>
+        <v>4607894.2</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2024,13 +2024,13 @@
         <v>119</v>
       </c>
       <c r="J44">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="K44">
-        <v>663.89</v>
+        <v>229850.62</v>
       </c>
       <c r="L44">
-        <v>39833.4</v>
+        <v>1838804.96</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2041,28 +2041,28 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
         <v>110</v>
       </c>
       <c r="E45" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I45" t="s">
         <v>119</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K45">
-        <v>209975.56</v>
+        <v>663.89</v>
       </c>
       <c r="L45">
-        <v>209975.56</v>
+        <v>39833.4</v>
       </c>
     </row>
     <row r="46" spans="1:12">

--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlopez\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{398EA981-CB44-4DBE-8D08-18C4ED10B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Valorizado" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="124">
   <si>
     <t>Categoría</t>
   </si>
@@ -58,15 +77,6 @@
     <t>Categoría producto</t>
   </si>
   <si>
-    <t>7059</t>
-  </si>
-  <si>
-    <t>235383</t>
-  </si>
-  <si>
-    <t>994349</t>
-  </si>
-  <si>
     <t>1824680C1</t>
   </si>
   <si>
@@ -82,15 +92,9 @@
     <t>3202C9129</t>
   </si>
   <si>
-    <t>363-4009/1613</t>
-  </si>
-  <si>
     <t>4302712/8398</t>
   </si>
   <si>
-    <t>7215/07</t>
-  </si>
-  <si>
     <t>9501/9471 2TOR</t>
   </si>
   <si>
@@ -106,21 +110,15 @@
     <t>R230072 EUCLID</t>
   </si>
   <si>
-    <t>VAD25 09 10</t>
-  </si>
-  <si>
     <t>WAB9700519502</t>
   </si>
   <si>
+    <t>X007785/ECL1942/SC</t>
+  </si>
+  <si>
     <t>X8870342</t>
   </si>
   <si>
-    <t>4302312</t>
-  </si>
-  <si>
-    <t>4304615</t>
-  </si>
-  <si>
     <t>128462/128947ARM</t>
   </si>
   <si>
@@ -145,15 +143,15 @@
     <t>R802689/R802447</t>
   </si>
   <si>
-    <t>4302670</t>
-  </si>
-  <si>
     <t>ES423L ELG/THK</t>
   </si>
   <si>
     <t>A7331</t>
   </si>
   <si>
+    <t>3278W335/43067</t>
+  </si>
+  <si>
     <t>1229K3001</t>
   </si>
   <si>
@@ -163,12 +161,12 @@
     <t>5556503/3MM</t>
   </si>
   <si>
-    <t>14897</t>
-  </si>
-  <si>
     <t>4303796/4301527WAP</t>
   </si>
   <si>
+    <t>126180WAP</t>
+  </si>
+  <si>
     <t>56929/500.946</t>
   </si>
   <si>
@@ -202,21 +200,18 @@
     <t>MERITOR</t>
   </si>
   <si>
-    <t>STEMCO</t>
-  </si>
-  <si>
     <t>MAHLE</t>
   </si>
   <si>
     <t>EUCLID</t>
   </si>
   <si>
-    <t>VADEN</t>
-  </si>
-  <si>
     <t>WABCO</t>
   </si>
   <si>
+    <t>TORCTITE</t>
+  </si>
+  <si>
     <t>EATON CLUTCH</t>
   </si>
   <si>
@@ -229,6 +224,9 @@
     <t>ELGIN</t>
   </si>
   <si>
+    <t>DAYCO</t>
+  </si>
+  <si>
     <t>WAP</t>
   </si>
   <si>
@@ -244,6 +242,9 @@
     <t>BOLSA SILLA CZ TODAS INTER</t>
   </si>
   <si>
+    <t>BOLSA SILLA CARE PANELA KW 2005...</t>
+  </si>
+  <si>
     <t>PISTA AXIAL EJE DE TOMA FS4205A</t>
   </si>
   <si>
@@ -265,15 +266,9 @@
     <t>EJE LATERAL TRAS 46160 ANTIPATINAJE RECT</t>
   </si>
   <si>
-    <t>TAPA NEGRA DEFENDER  PASTA 5 1/2" GRANDE</t>
-  </si>
-  <si>
     <t>RODILLO TREN FIJO PARTE TRAS - TODAS 18</t>
   </si>
   <si>
-    <t>BOLSA SUSPENSION CABINA FREIGTHLINER</t>
-  </si>
-  <si>
     <t>BOLSA TAN10.12ANx5.87CCx24.50AL+7.88D+2T</t>
   </si>
   <si>
@@ -289,12 +284,12 @@
     <t>TERMINAL 2090 IZQUIERDA EUCLID</t>
   </si>
   <si>
-    <t>CULATA COMPLETA BUS RUNNER MOTOR ISL2,</t>
-  </si>
-  <si>
     <t>EMPAQUETADURA SERVO EMBRAGUE RUNNER</t>
   </si>
   <si>
+    <t>ABRAZADERA EXOSTO 5"</t>
+  </si>
+  <si>
     <t>HINO PIN MONO REDUCTOR</t>
   </si>
   <si>
@@ -337,6 +332,9 @@
     <t>PATA SINCRONIZADOR K-3492</t>
   </si>
   <si>
+    <t>CRUCETA ESCUALIZACION 46160</t>
+  </si>
+  <si>
     <t>ARANDELA SATELITE ESCUALIZACION 46160</t>
   </si>
   <si>
@@ -349,9 +347,15 @@
     <t>RESORTE</t>
   </si>
   <si>
+    <t>CORREA PARA COLUMBIA SERIE60 12LT</t>
+  </si>
+  <si>
     <t>PIÑON DE 4TA EJE CORREDIZO 4205</t>
   </si>
   <si>
+    <t>ARANDELA SATELITE DIVISOR 46 LBS PLANA</t>
+  </si>
+  <si>
     <t>TEFLON SUSPENSIÓN HOJA ZETA</t>
   </si>
   <si>
@@ -373,6 +377,9 @@
     <t>WAP/TRANSMISION</t>
   </si>
   <si>
+    <t>WAP/DIFERENCIAL-CARDAN</t>
+  </si>
+  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -391,20 +398,20 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 08:45:56</t>
+    <t>Período: 30/11/2025 12:29:18</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 30/10/2025 08:46:54</t>
+    <t>Fecha y hora de generación: 01/11/2025 12:29:51</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,10 +504,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -508,28 +521,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -567,7 +583,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -601,6 +617,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -635,9 +652,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -810,130 +828,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="6" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="I7" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="6" t="s">
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
-        <v>14</v>
+      <c r="B10" s="7">
+        <v>7059</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -945,283 +963,283 @@
         <v>111634.66</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
+      <c r="B11" s="7">
+        <v>7086</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>27548.37</v>
+        <v>140713.63</v>
       </c>
       <c r="L11">
-        <v>55096.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>140713.63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
+      <c r="B12" s="7">
+        <v>235383</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J12">
         <v>2</v>
       </c>
       <c r="K12">
-        <v>287070.62</v>
+        <v>27548.37</v>
       </c>
       <c r="L12">
-        <v>574141.24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>55096.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>17</v>
+      <c r="B13" s="7">
+        <v>994349</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J13">
         <v>2</v>
       </c>
       <c r="K13">
+        <v>287070.62</v>
+      </c>
+      <c r="L13">
+        <v>574141.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" t="s">
+        <v>115</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
         <v>20866.91</v>
       </c>
-      <c r="L13">
+      <c r="L14">
         <v>41733.82</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15">
+        <v>69586.600000000006</v>
+      </c>
+      <c r="L15">
+        <v>347933</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" t="s">
+        <v>115</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <v>177348.88</v>
+      </c>
+      <c r="L16">
+        <v>354697.76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17">
+        <v>7</v>
+      </c>
+      <c r="K17">
+        <v>70360.37</v>
+      </c>
+      <c r="L17">
+        <v>492522.59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" t="s">
-        <v>119</v>
-      </c>
-      <c r="J14">
-        <v>5</v>
-      </c>
-      <c r="K14">
-        <v>69586.60000000001</v>
-      </c>
-      <c r="L14">
-        <v>347933</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" t="s">
+        <v>115</v>
+      </c>
+      <c r="J18">
+        <v>12</v>
+      </c>
+      <c r="K18">
+        <v>525495.80000000005</v>
+      </c>
+      <c r="L18">
+        <v>6305949.5999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
         <v>19</v>
       </c>
-      <c r="C15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" t="s">
-        <v>119</v>
-      </c>
-      <c r="J15">
-        <v>2</v>
-      </c>
-      <c r="K15">
-        <v>177348.88</v>
-      </c>
-      <c r="L15">
-        <v>354697.76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" t="s">
-        <v>119</v>
-      </c>
-      <c r="J16">
-        <v>4</v>
-      </c>
-      <c r="K16">
-        <v>70851.95</v>
-      </c>
-      <c r="L16">
-        <v>283407.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" t="s">
-        <v>119</v>
-      </c>
-      <c r="J17">
-        <v>12</v>
-      </c>
-      <c r="K17">
-        <v>525495.8</v>
-      </c>
-      <c r="L17">
-        <v>6305949.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" t="s">
-        <v>119</v>
-      </c>
-      <c r="J18">
-        <v>2</v>
-      </c>
-      <c r="K18">
-        <v>41542.9</v>
-      </c>
-      <c r="L18">
-        <v>83085.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I19" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -1233,731 +1251,731 @@
         <v>209726.48</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
       <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I20" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>558922.19999999995</v>
+      </c>
+      <c r="L20">
+        <v>558922.19999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" t="s">
+        <v>115</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>109890.41</v>
+      </c>
+      <c r="L21">
+        <v>219780.82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>237833.89</v>
+      </c>
+      <c r="L22">
+        <v>237833.89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" t="s">
+        <v>115</v>
+      </c>
+      <c r="J23">
+        <v>20</v>
+      </c>
+      <c r="K23">
+        <v>297747.46999999997</v>
+      </c>
+      <c r="L23">
+        <v>5954949.4000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
         <v>24</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="I20" t="s">
-        <v>119</v>
-      </c>
-      <c r="J20">
-        <v>2</v>
-      </c>
-      <c r="K20">
-        <v>91384.38</v>
-      </c>
-      <c r="L20">
-        <v>182768.76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" t="s">
-        <v>119</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>558922.2</v>
-      </c>
-      <c r="L21">
-        <v>558922.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-      <c r="I22" t="s">
-        <v>119</v>
-      </c>
-      <c r="J22">
-        <v>2</v>
-      </c>
-      <c r="K22">
-        <v>109890.41</v>
-      </c>
-      <c r="L22">
-        <v>219780.82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" t="s">
-        <v>63</v>
-      </c>
-      <c r="I23" t="s">
-        <v>119</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>237833.89</v>
-      </c>
-      <c r="L23">
-        <v>237833.89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
       </c>
       <c r="C24" t="s">
         <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J24">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K24">
-        <v>297747.47</v>
+        <v>94848.23</v>
       </c>
       <c r="L24">
-        <v>5954949.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>189696.46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>94848.23</v>
+        <v>150117.48000000001</v>
       </c>
       <c r="L25">
-        <v>189696.46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>150117.48000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="I26" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>348949.42</v>
+        <v>25537.919999999998</v>
       </c>
       <c r="L26">
-        <v>348949.42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>25537.919999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="I27" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J27">
+        <v>5</v>
+      </c>
+      <c r="K27">
+        <v>3641.01</v>
+      </c>
+      <c r="L27">
+        <v>18205.05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="7">
+        <v>4302312</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" t="s">
+        <v>115</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>20800.669999999998</v>
+      </c>
+      <c r="L28">
+        <v>41601.339999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="7">
+        <v>4304615</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" t="s">
+        <v>115</v>
+      </c>
+      <c r="J29">
+        <v>47</v>
+      </c>
+      <c r="K29">
+        <v>3936.75</v>
+      </c>
+      <c r="L29">
+        <v>185027.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" t="s">
+        <v>115</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
+        <v>312918.09000000003</v>
+      </c>
+      <c r="L30">
+        <v>938754.27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" t="s">
+        <v>115</v>
+      </c>
+      <c r="J31">
         <v>1</v>
       </c>
-      <c r="K27">
-        <v>150117.48</v>
-      </c>
-      <c r="L27">
-        <v>150117.48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" t="s">
-        <v>119</v>
-      </c>
-      <c r="J28">
-        <v>5</v>
-      </c>
-      <c r="K28">
-        <v>3641.01</v>
-      </c>
-      <c r="L28">
-        <v>18205.05</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-      <c r="I29" t="s">
-        <v>119</v>
-      </c>
-      <c r="J29">
-        <v>2</v>
-      </c>
-      <c r="K29">
-        <v>20800.67</v>
-      </c>
-      <c r="L29">
-        <v>41601.34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-      <c r="I30" t="s">
-        <v>119</v>
-      </c>
-      <c r="J30">
-        <v>47</v>
-      </c>
-      <c r="K30">
-        <v>3936.75</v>
-      </c>
-      <c r="L30">
-        <v>185027.25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" t="s">
-        <v>96</v>
-      </c>
-      <c r="E31" t="s">
-        <v>56</v>
-      </c>
-      <c r="F31" t="s">
-        <v>67</v>
-      </c>
-      <c r="I31" t="s">
-        <v>119</v>
-      </c>
-      <c r="J31">
-        <v>3</v>
-      </c>
       <c r="K31">
-        <v>312918.09</v>
+        <v>206249.01</v>
       </c>
       <c r="L31">
-        <v>938754.27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>206249.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I32" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32">
-        <v>206249.01</v>
+        <v>2444357.96</v>
       </c>
       <c r="L32">
-        <v>206249.01</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>2444357.96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I33" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <v>2444357.96</v>
+        <v>216538.69</v>
       </c>
       <c r="L33">
-        <v>2444357.96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+        <v>216538.69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F34" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="K34">
-        <v>216538.69</v>
+        <v>286676.26</v>
       </c>
       <c r="L34">
-        <v>216538.69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>286676.26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E35" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I35" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J35">
+        <v>792</v>
+      </c>
+      <c r="K35">
+        <v>18048.240000000002</v>
+      </c>
+      <c r="L35">
+        <v>14294206.08</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" t="s">
+        <v>54</v>
+      </c>
+      <c r="I36" t="s">
+        <v>115</v>
+      </c>
+      <c r="J36">
+        <v>60</v>
+      </c>
+      <c r="K36">
+        <v>20614.169999999998</v>
+      </c>
+      <c r="L36">
+        <v>1236850.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" t="s">
+        <v>54</v>
+      </c>
+      <c r="I37" t="s">
+        <v>115</v>
+      </c>
+      <c r="J37">
+        <v>13</v>
+      </c>
+      <c r="K37">
+        <v>162426.15</v>
+      </c>
+      <c r="L37">
+        <v>2111539.9500000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="7">
+        <v>4302670</v>
+      </c>
+      <c r="C38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" t="s">
+        <v>49</v>
+      </c>
+      <c r="I38" t="s">
+        <v>115</v>
+      </c>
+      <c r="J38">
         <v>1</v>
       </c>
-      <c r="K35">
-        <v>286676.26</v>
-      </c>
-      <c r="L35">
-        <v>286676.26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" t="s">
-        <v>69</v>
-      </c>
-      <c r="F36" t="s">
-        <v>69</v>
-      </c>
-      <c r="I36" t="s">
-        <v>119</v>
-      </c>
-      <c r="J36">
-        <v>792</v>
-      </c>
-      <c r="K36">
-        <v>18048.24</v>
-      </c>
-      <c r="L36">
-        <v>14294206.08</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" t="s">
-        <v>61</v>
-      </c>
-      <c r="D37" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" t="s">
-        <v>61</v>
-      </c>
-      <c r="F37" t="s">
-        <v>61</v>
-      </c>
-      <c r="I37" t="s">
-        <v>119</v>
-      </c>
-      <c r="J37">
-        <v>60</v>
-      </c>
-      <c r="K37">
-        <v>20614.17</v>
-      </c>
-      <c r="L37">
-        <v>1236850.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" t="s">
-        <v>61</v>
-      </c>
-      <c r="D38" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" t="s">
-        <v>61</v>
-      </c>
-      <c r="I38" t="s">
-        <v>119</v>
-      </c>
-      <c r="J38">
-        <v>13</v>
-      </c>
       <c r="K38">
-        <v>162426.15</v>
+        <v>261801.89</v>
       </c>
       <c r="L38">
-        <v>2111539.95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+        <v>261801.89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E39" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F39" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I39" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="K39">
-        <v>261801.89</v>
+        <v>75557.81</v>
       </c>
       <c r="L39">
-        <v>261801.89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
+        <v>75557.81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="F40" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="I40" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J40">
+        <v>19</v>
+      </c>
+      <c r="K40">
+        <v>122009.29</v>
+      </c>
+      <c r="L40">
+        <v>2318176.5099999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" t="s">
+        <v>54</v>
+      </c>
+      <c r="I41" t="s">
+        <v>115</v>
+      </c>
+      <c r="J41">
         <v>1</v>
       </c>
-      <c r="K40">
-        <v>75557.81</v>
-      </c>
-      <c r="L40">
-        <v>75557.81</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" t="s">
-        <v>106</v>
-      </c>
-      <c r="E41" t="s">
-        <v>56</v>
-      </c>
-      <c r="F41" t="s">
-        <v>56</v>
-      </c>
-      <c r="I41" t="s">
-        <v>119</v>
-      </c>
-      <c r="J41">
-        <v>19</v>
-      </c>
       <c r="K41">
-        <v>122009.29</v>
+        <v>114045.11</v>
       </c>
       <c r="L41">
-        <v>2318176.51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+        <v>114045.11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="I42" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J42">
         <v>360</v>
@@ -1966,30 +1984,30 @@
         <v>3512.14</v>
       </c>
       <c r="L42">
-        <v>1264370.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
+        <v>1264370.3999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E43" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F43" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="I43" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J43">
         <v>364</v>
@@ -2001,27 +2019,27 @@
         <v>4607894.2</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E44" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I44" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J44">
         <v>8</v>
@@ -2033,27 +2051,27 @@
         <v>1838804.96</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>12</v>
       </c>
-      <c r="B45" t="s">
-        <v>49</v>
+      <c r="B45" s="7">
+        <v>14897</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F45" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J45">
         <v>60</v>
@@ -2065,163 +2083,227 @@
         <v>39833.4</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>12</v>
       </c>
-      <c r="B46" t="s">
-        <v>50</v>
+      <c r="B46" s="7">
+        <v>17515</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E46" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F46" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="I46" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="K46">
-        <v>163002.7</v>
+        <v>12173.17</v>
       </c>
       <c r="L46">
-        <v>163002.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+        <v>12173.17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="I47" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="K47">
+        <v>163002.70000000001</v>
+      </c>
+      <c r="L47">
+        <v>163002.70000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" t="s">
+        <v>64</v>
+      </c>
+      <c r="F48" t="s">
+        <v>114</v>
+      </c>
+      <c r="I48" t="s">
+        <v>115</v>
+      </c>
+      <c r="J48">
+        <v>4</v>
+      </c>
+      <c r="K48">
+        <v>9156.48</v>
+      </c>
+      <c r="L48">
+        <v>36625.919999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" t="s">
+        <v>107</v>
+      </c>
+      <c r="E49" t="s">
+        <v>65</v>
+      </c>
+      <c r="F49" t="s">
+        <v>65</v>
+      </c>
+      <c r="I49" t="s">
+        <v>115</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
         <v>15384.67</v>
       </c>
-      <c r="L47">
+      <c r="L49">
         <v>15384.67</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
-      <c r="A48" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48" t="s">
-        <v>73</v>
-      </c>
-      <c r="D48" t="s">
-        <v>113</v>
-      </c>
-      <c r="E48" t="s">
-        <v>73</v>
-      </c>
-      <c r="F48" t="s">
-        <v>73</v>
-      </c>
-      <c r="I48" t="s">
-        <v>119</v>
-      </c>
-      <c r="J48">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D50" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" t="s">
+        <v>66</v>
+      </c>
+      <c r="F50" t="s">
+        <v>66</v>
+      </c>
+      <c r="I50" t="s">
+        <v>115</v>
+      </c>
+      <c r="J50">
         <v>2</v>
       </c>
-      <c r="K48">
+      <c r="K50">
         <v>193066.84</v>
       </c>
-      <c r="L48">
+      <c r="L50">
         <v>386133.68</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
-      <c r="A49" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" t="s">
-        <v>73</v>
-      </c>
-      <c r="D49" t="s">
-        <v>114</v>
-      </c>
-      <c r="E49" t="s">
-        <v>73</v>
-      </c>
-      <c r="F49" t="s">
-        <v>73</v>
-      </c>
-      <c r="I49" t="s">
-        <v>119</v>
-      </c>
-      <c r="J49">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" t="s">
+        <v>109</v>
+      </c>
+      <c r="E51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51" t="s">
+        <v>66</v>
+      </c>
+      <c r="I51" t="s">
+        <v>115</v>
+      </c>
+      <c r="J51">
         <v>5</v>
       </c>
-      <c r="K49">
+      <c r="K51">
         <v>26517.61</v>
       </c>
-      <c r="L49">
-        <v>132588.05</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" t="s">
-        <v>54</v>
-      </c>
-      <c r="C50" t="s">
-        <v>74</v>
-      </c>
-      <c r="D50" t="s">
-        <v>115</v>
-      </c>
-      <c r="E50" t="s">
-        <v>117</v>
-      </c>
-      <c r="F50" t="s">
-        <v>117</v>
-      </c>
-      <c r="I50" t="s">
-        <v>119</v>
-      </c>
-      <c r="J50">
+      <c r="L51">
+        <v>132588.04999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" t="s">
+        <v>110</v>
+      </c>
+      <c r="E52" t="s">
+        <v>112</v>
+      </c>
+      <c r="F52" t="s">
+        <v>112</v>
+      </c>
+      <c r="I52" t="s">
+        <v>115</v>
+      </c>
+      <c r="J52">
         <v>1</v>
       </c>
-      <c r="K50">
+      <c r="K52">
         <v>39099.54</v>
       </c>
-      <c r="L50">
+      <c r="L52">
         <v>39099.54</v>
       </c>
     </row>

--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -1,39 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlopez\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{398EA981-CB44-4DBE-8D08-18C4ED10B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Valorizado" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="130">
   <si>
     <t>Categoría</t>
   </si>
@@ -77,6 +58,18 @@
     <t>Categoría producto</t>
   </si>
   <si>
+    <t>7059</t>
+  </si>
+  <si>
+    <t>7086</t>
+  </si>
+  <si>
+    <t>235383</t>
+  </si>
+  <si>
+    <t>994349</t>
+  </si>
+  <si>
     <t>1824680C1</t>
   </si>
   <si>
@@ -119,6 +112,12 @@
     <t>X8870342</t>
   </si>
   <si>
+    <t>4302312</t>
+  </si>
+  <si>
+    <t>4304615</t>
+  </si>
+  <si>
     <t>128462/128947ARM</t>
   </si>
   <si>
@@ -143,6 +142,9 @@
     <t>R802689/R802447</t>
   </si>
   <si>
+    <t>4302670</t>
+  </si>
+  <si>
     <t>ES423L ELG/THK</t>
   </si>
   <si>
@@ -161,7 +163,10 @@
     <t>5556503/3MM</t>
   </si>
   <si>
-    <t>4303796/4301527WAP</t>
+    <t>14897</t>
+  </si>
+  <si>
+    <t>17515</t>
   </si>
   <si>
     <t>126180WAP</t>
@@ -350,9 +355,6 @@
     <t>CORREA PARA COLUMBIA SERIE60 12LT</t>
   </si>
   <si>
-    <t>PIÑON DE 4TA EJE CORREDIZO 4205</t>
-  </si>
-  <si>
     <t>ARANDELA SATELITE DIVISOR 46 LBS PLANA</t>
   </si>
   <si>
@@ -374,9 +376,6 @@
     <t>USA</t>
   </si>
   <si>
-    <t>WAP/TRANSMISION</t>
-  </si>
-  <si>
     <t>WAP/DIFERENCIAL-CARDAN</t>
   </si>
   <si>
@@ -398,20 +397,20 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/11/2025 12:29:18</t>
+    <t>Período: 29/11/2025 22:19:30</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 01/11/2025 12:29:51</t>
+    <t>Fecha y hora de generación: 04/11/2025 22:20:04</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,16 +503,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -521,31 +514,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -583,7 +573,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -617,7 +607,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -652,10 +641,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -828,130 +816,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="I7" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I7" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="7">
-        <v>7059</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" t="s">
-        <v>111</v>
-      </c>
       <c r="F10" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="I10" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -963,27 +951,27 @@
         <v>111634.66</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="7">
-        <v>7086</v>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I11" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -995,27 +983,27 @@
         <v>140713.63</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="7">
-        <v>235383</v>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1027,27 +1015,27 @@
         <v>55096.74</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7">
-        <v>994349</v>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1059,27 +1047,27 @@
         <v>574141.24</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I14" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1091,59 +1079,59 @@
         <v>41733.82</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I15" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J15">
         <v>5</v>
       </c>
       <c r="K15">
-        <v>69586.600000000006</v>
+        <v>69586.60000000001</v>
       </c>
       <c r="L15">
         <v>347933</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -1155,27 +1143,27 @@
         <v>354697.76</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -1187,59 +1175,59 @@
         <v>492522.59</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I18" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J18">
         <v>12</v>
       </c>
       <c r="K18">
-        <v>525495.80000000005</v>
+        <v>525495.8</v>
       </c>
       <c r="L18">
-        <v>6305949.5999999996</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>6305949.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I19" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -1251,59 +1239,59 @@
         <v>209726.48</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I20" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
-        <v>558922.19999999995</v>
+        <v>558922.2</v>
       </c>
       <c r="L20">
-        <v>558922.19999999995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>558922.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I21" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -1315,27 +1303,27 @@
         <v>219780.82</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1347,59 +1335,59 @@
         <v>237833.89</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J23">
         <v>20</v>
       </c>
       <c r="K23">
-        <v>297747.46999999997</v>
+        <v>297747.47</v>
       </c>
       <c r="L23">
-        <v>5954949.4000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>5954949.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -1411,91 +1399,91 @@
         <v>189696.46</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I25" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>150117.48000000001</v>
+        <v>150117.48</v>
       </c>
       <c r="L25">
-        <v>150117.48000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>150117.48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>25537.919999999998</v>
+        <v>25537.92</v>
       </c>
       <c r="L26">
-        <v>25537.919999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>25537.92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I27" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -1507,59 +1495,59 @@
         <v>18205.05</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="7">
-        <v>4302312</v>
+      <c r="B28" t="s">
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I28" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J28">
         <v>2</v>
       </c>
       <c r="K28">
-        <v>20800.669999999998</v>
+        <v>20800.67</v>
       </c>
       <c r="L28">
-        <v>41601.339999999997</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>41601.34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="7">
-        <v>4304615</v>
+      <c r="B29" t="s">
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F29" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I29" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J29">
         <v>47</v>
@@ -1571,59 +1559,59 @@
         <v>185027.25</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I30" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J30">
         <v>3</v>
       </c>
       <c r="K30">
-        <v>312918.09000000003</v>
+        <v>312918.09</v>
       </c>
       <c r="L30">
         <v>938754.27</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F31" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I31" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1635,27 +1623,27 @@
         <v>206249.01</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1667,27 +1655,27 @@
         <v>2444357.96</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1699,27 +1687,27 @@
         <v>216538.69</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F34" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I34" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1731,91 +1719,91 @@
         <v>286676.26</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F35" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I35" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J35">
         <v>792</v>
       </c>
       <c r="K35">
-        <v>18048.240000000002</v>
+        <v>18048.24</v>
       </c>
       <c r="L35">
         <v>14294206.08</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J36">
         <v>60</v>
       </c>
       <c r="K36">
-        <v>20614.169999999998</v>
+        <v>20614.17</v>
       </c>
       <c r="L36">
         <v>1236850.2</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I37" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J37">
         <v>13</v>
@@ -1824,30 +1812,30 @@
         <v>162426.15</v>
       </c>
       <c r="L37">
-        <v>2111539.9500000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2111539.95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="7">
-        <v>4302670</v>
+      <c r="B38" t="s">
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D38" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F38" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I38" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -1859,27 +1847,27 @@
         <v>261801.89</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F39" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I39" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -1891,27 +1879,27 @@
         <v>75557.81</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F40" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I40" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J40">
         <v>19</v>
@@ -1920,30 +1908,30 @@
         <v>122009.29</v>
       </c>
       <c r="L40">
-        <v>2318176.5099999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2318176.51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E41" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I41" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -1955,27 +1943,27 @@
         <v>114045.11</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D42" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E42" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I42" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J42">
         <v>360</v>
@@ -1984,30 +1972,30 @@
         <v>3512.14</v>
       </c>
       <c r="L42">
-        <v>1264370.3999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1264370.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
         <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I43" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J43">
         <v>364</v>
@@ -2019,27 +2007,27 @@
         <v>4607894.2</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D44" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F44" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J44">
         <v>8</v>
@@ -2051,27 +2039,27 @@
         <v>1838804.96</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="7">
-        <v>14897</v>
+      <c r="B45" t="s">
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F45" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I45" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J45">
         <v>60</v>
@@ -2083,27 +2071,27 @@
         <v>39833.4</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="7">
-        <v>17515</v>
+      <c r="B46" t="s">
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E46" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F46" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I46" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2115,195 +2103,163 @@
         <v>12173.17</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D47" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E47" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F47" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I47" t="s">
+        <v>121</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+      <c r="K47">
+        <v>9156.48</v>
+      </c>
+      <c r="L47">
+        <v>36625.92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48" t="s">
+        <v>73</v>
+      </c>
+      <c r="I48" t="s">
+        <v>121</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>15384.67</v>
+      </c>
+      <c r="L48">
+        <v>15384.67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" t="s">
         <v>115</v>
       </c>
-      <c r="J47">
+      <c r="E49" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" t="s">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s">
+        <v>121</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="K49">
+        <v>193066.84</v>
+      </c>
+      <c r="L49">
+        <v>386133.68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" t="s">
+        <v>74</v>
+      </c>
+      <c r="F50" t="s">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s">
+        <v>121</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
+      <c r="K50">
+        <v>26517.61</v>
+      </c>
+      <c r="L50">
+        <v>132588.05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51" t="s">
+        <v>119</v>
+      </c>
+      <c r="F51" t="s">
+        <v>119</v>
+      </c>
+      <c r="I51" t="s">
+        <v>121</v>
+      </c>
+      <c r="J51">
         <v>1</v>
       </c>
-      <c r="K47">
-        <v>163002.70000000001</v>
-      </c>
-      <c r="L47">
-        <v>163002.70000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" t="s">
-        <v>106</v>
-      </c>
-      <c r="E48" t="s">
-        <v>64</v>
-      </c>
-      <c r="F48" t="s">
-        <v>114</v>
-      </c>
-      <c r="I48" t="s">
-        <v>115</v>
-      </c>
-      <c r="J48">
-        <v>4</v>
-      </c>
-      <c r="K48">
-        <v>9156.48</v>
-      </c>
-      <c r="L48">
-        <v>36625.919999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" t="s">
-        <v>65</v>
-      </c>
-      <c r="D49" t="s">
-        <v>107</v>
-      </c>
-      <c r="E49" t="s">
-        <v>65</v>
-      </c>
-      <c r="F49" t="s">
-        <v>65</v>
-      </c>
-      <c r="I49" t="s">
-        <v>115</v>
-      </c>
-      <c r="J49">
-        <v>1</v>
-      </c>
-      <c r="K49">
-        <v>15384.67</v>
-      </c>
-      <c r="L49">
-        <v>15384.67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" t="s">
-        <v>45</v>
-      </c>
-      <c r="C50" t="s">
-        <v>66</v>
-      </c>
-      <c r="D50" t="s">
-        <v>108</v>
-      </c>
-      <c r="E50" t="s">
-        <v>66</v>
-      </c>
-      <c r="F50" t="s">
-        <v>66</v>
-      </c>
-      <c r="I50" t="s">
-        <v>115</v>
-      </c>
-      <c r="J50">
-        <v>2</v>
-      </c>
-      <c r="K50">
-        <v>193066.84</v>
-      </c>
-      <c r="L50">
-        <v>386133.68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" t="s">
-        <v>66</v>
-      </c>
-      <c r="D51" t="s">
-        <v>109</v>
-      </c>
-      <c r="E51" t="s">
-        <v>66</v>
-      </c>
-      <c r="F51" t="s">
-        <v>66</v>
-      </c>
-      <c r="I51" t="s">
-        <v>115</v>
-      </c>
-      <c r="J51">
-        <v>5</v>
-      </c>
       <c r="K51">
-        <v>26517.61</v>
+        <v>39099.54</v>
       </c>
       <c r="L51">
-        <v>132588.04999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" t="s">
-        <v>110</v>
-      </c>
-      <c r="E52" t="s">
-        <v>112</v>
-      </c>
-      <c r="F52" t="s">
-        <v>112</v>
-      </c>
-      <c r="I52" t="s">
-        <v>115</v>
-      </c>
-      <c r="J52">
-        <v>1</v>
-      </c>
-      <c r="K52">
-        <v>39099.54</v>
-      </c>
-      <c r="L52">
         <v>39099.54</v>
       </c>
     </row>

--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="131">
   <si>
     <t>Categoría</t>
   </si>
@@ -61,12 +61,18 @@
     <t>7059</t>
   </si>
   <si>
+    <t>7086</t>
+  </si>
+  <si>
     <t>235383</t>
   </si>
   <si>
     <t>994349</t>
   </si>
   <si>
+    <t>4306314</t>
+  </si>
+  <si>
     <t>1824680C1</t>
   </si>
   <si>
@@ -76,21 +82,18 @@
     <t>20382B</t>
   </si>
   <si>
+    <t>22028B/4305659</t>
+  </si>
+  <si>
     <t>2252-1D</t>
   </si>
   <si>
     <t>3202C9129</t>
   </si>
   <si>
-    <t>363-4009/1613</t>
-  </si>
-  <si>
     <t>4302712/8398</t>
   </si>
   <si>
-    <t>7215/07</t>
-  </si>
-  <si>
     <t>9501/9471 2TOR</t>
   </si>
   <si>
@@ -100,21 +103,24 @@
     <t>JI21380/J&amp;RI-2304/4BT MAH</t>
   </si>
   <si>
+    <t>K3245</t>
+  </si>
+  <si>
     <t>K3367</t>
   </si>
   <si>
     <t>R230072 EUCLID</t>
   </si>
   <si>
-    <t>VAD25 09 10</t>
-  </si>
-  <si>
     <t>WAB9700519502</t>
   </si>
   <si>
     <t>X8870342</t>
   </si>
   <si>
+    <t>127760</t>
+  </si>
+  <si>
     <t>4302312</t>
   </si>
   <si>
@@ -127,7 +133,7 @@
     <t>20461B/5903</t>
   </si>
   <si>
-    <t>B39882-1</t>
+    <t>205C119</t>
   </si>
   <si>
     <t>HS54253/1817255 CLE</t>
@@ -154,6 +160,9 @@
     <t>A7331</t>
   </si>
   <si>
+    <t>3278W335/43067</t>
+  </si>
+  <si>
     <t>1229K3001</t>
   </si>
   <si>
@@ -166,7 +175,7 @@
     <t>14897</t>
   </si>
   <si>
-    <t>4303796/4301527WAP</t>
+    <t>17515</t>
   </si>
   <si>
     <t>56929/500.946</t>
@@ -202,18 +211,12 @@
     <t>MERITOR</t>
   </si>
   <si>
-    <t>STEMCO</t>
-  </si>
-  <si>
     <t>MAHLE</t>
   </si>
   <si>
     <t>EUCLID</t>
   </si>
   <si>
-    <t>VADEN</t>
-  </si>
-  <si>
     <t>WABCO</t>
   </si>
   <si>
@@ -229,7 +232,7 @@
     <t>ELGIN</t>
   </si>
   <si>
-    <t>WAP</t>
+    <t>DAYCO</t>
   </si>
   <si>
     <t>SAMPA</t>
@@ -244,12 +247,18 @@
     <t>BOLSA SILLA CZ TODAS INTER</t>
   </si>
   <si>
+    <t>BOLSA SILLA CARE PANELA KW 2005...</t>
+  </si>
+  <si>
     <t>PISTA AXIAL EJE DE TOMA FS4205A</t>
   </si>
   <si>
     <t>ASBESTO FAN CLUTCH DRIVE MASTER 8" JGOX2</t>
   </si>
   <si>
+    <t>ACOPLE ESTRIADO BALINERA 510 MONO 16E318</t>
+  </si>
+  <si>
     <t>ROTOR TODAS LAS VALVULAS DT466 ELECTRONI</t>
   </si>
   <si>
@@ -259,21 +268,18 @@
     <t>PIÑÓN 2DA TREN FIJO 14715/16915</t>
   </si>
   <si>
+    <t>PIÑON 4TA RTO 11609</t>
+  </si>
+  <si>
     <t>VALVULA NIVELADORA TANQUE COMBUSTIBLE</t>
   </si>
   <si>
     <t>EJE LATERAL TRAS 46160 ANTIPATINAJE RECT</t>
   </si>
   <si>
-    <t>TAPA NEGRA DEFENDER  PASTA 5 1/2" GRANDE</t>
-  </si>
-  <si>
     <t>RODILLO TREN FIJO PARTE TRAS - TODAS 18</t>
   </si>
   <si>
-    <t>BOLSA SUSPENSION CABINA FREIGTHLINER</t>
-  </si>
-  <si>
     <t>BOLSA TAN10.12ANx5.87CCx24.50AL+7.88D+2T</t>
   </si>
   <si>
@@ -283,21 +289,24 @@
     <t>EMPAQUETADURA INFERIOR CUMM 3802375 4BT</t>
   </si>
   <si>
+    <t>KIT MODULO CAJA (JGO X2) FR/FRO</t>
+  </si>
+  <si>
     <t>KIT BOMBA ACEITE CAJA JGOX3 14718/918/16</t>
   </si>
   <si>
     <t>TERMINAL 2090 IZQUIERDA EUCLID</t>
   </si>
   <si>
-    <t>CULATA COMPLETA BUS RUNNER MOTOR ISL2,</t>
-  </si>
-  <si>
     <t>EMPAQUETADURA SERVO EMBRAGUE RUNNER</t>
   </si>
   <si>
     <t>HINO PIN MONO REDUCTOR</t>
   </si>
   <si>
+    <t>FRENO EMBRAGUE 2"</t>
+  </si>
+  <si>
     <t>ARANDELA PLANA PIÑÓN RVSO FR/FRO TODAS</t>
   </si>
   <si>
@@ -310,7 +319,7 @@
     <t>PIÑÓN 4TA TREN FIJO 14715/16915</t>
   </si>
   <si>
-    <t>CORONA Y SPEED DP 9X41</t>
+    <t>TORNILLO EMBRAGUE 308925-82</t>
   </si>
   <si>
     <t>EMPAQUETADURA SUPERIOR DT 360</t>
@@ -337,6 +346,9 @@
     <t>PATA SINCRONIZADOR K-3492</t>
   </si>
   <si>
+    <t>CRUCETA ESCUALIZACION 46160</t>
+  </si>
+  <si>
     <t>ARANDELA SATELITE ESCUALIZACION 46160</t>
   </si>
   <si>
@@ -349,7 +361,7 @@
     <t>RESORTE</t>
   </si>
   <si>
-    <t>PIÑON DE 4TA EJE CORREDIZO 4205</t>
+    <t>CORREA PARA COLUMBIA SERIE60 12LT</t>
   </si>
   <si>
     <t>TEFLON SUSPENSIÓN HOJA ZETA</t>
@@ -370,9 +382,6 @@
     <t>USA</t>
   </si>
   <si>
-    <t>WAP/TRANSMISION</t>
-  </si>
-  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -391,13 +400,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 08:45:56</t>
+    <t>Período: 30/11/2025 08:47:22</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 30/10/2025 08:46:54</t>
+    <t>Fecha y hora de generación: 26/11/2025 08:48:32</t>
   </si>
 </sst>
 </file>
@@ -811,28 +820,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -848,7 +857,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -864,12 +873,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -921,19 +930,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -953,28 +962,28 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>27548.37</v>
+        <v>140713.63</v>
       </c>
       <c r="L11">
-        <v>55096.74</v>
+        <v>140713.63</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -985,28 +994,28 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J12">
         <v>2</v>
       </c>
       <c r="K12">
-        <v>287070.62</v>
+        <v>27548.37</v>
       </c>
       <c r="L12">
-        <v>574141.24</v>
+        <v>55096.74</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1017,28 +1026,28 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J13">
         <v>2</v>
       </c>
       <c r="K13">
-        <v>20866.91</v>
+        <v>287070.62</v>
       </c>
       <c r="L13">
-        <v>41733.82</v>
+        <v>574141.24</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1052,7 +1061,7 @@
         <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
         <v>59</v>
@@ -1061,16 +1070,16 @@
         <v>59</v>
       </c>
       <c r="I14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>69586.60000000001</v>
+        <v>57941.1</v>
       </c>
       <c r="L14">
-        <v>347933</v>
+        <v>173823.3</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1081,28 +1090,28 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J15">
         <v>2</v>
       </c>
       <c r="K15">
-        <v>177348.88</v>
+        <v>20866.91</v>
       </c>
       <c r="L15">
-        <v>354697.76</v>
+        <v>41733.82</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1113,28 +1122,28 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>70851.95</v>
+        <v>69586.60000000001</v>
       </c>
       <c r="L16">
-        <v>283407.8</v>
+        <v>347933</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1145,28 +1154,28 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J17">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>525495.8</v>
+        <v>177348.88</v>
       </c>
       <c r="L17">
-        <v>6305949.6</v>
+        <v>354697.76</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1177,28 +1186,28 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>41542.9</v>
+        <v>241211.27</v>
       </c>
       <c r="L18">
-        <v>83085.8</v>
+        <v>241211.27</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1209,28 +1218,28 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>52431.62</v>
+        <v>70360.37</v>
       </c>
       <c r="L19">
-        <v>209726.48</v>
+        <v>492522.59</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1241,28 +1250,28 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K20">
-        <v>91384.38</v>
+        <v>525495.8</v>
       </c>
       <c r="L20">
-        <v>182768.76</v>
+        <v>6305949.6</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1273,28 +1282,28 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>558922.2</v>
+        <v>52431.62</v>
       </c>
       <c r="L21">
-        <v>558922.2</v>
+        <v>209726.48</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1305,28 +1314,28 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I22" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>109890.41</v>
+        <v>558922.2</v>
       </c>
       <c r="L22">
-        <v>219780.82</v>
+        <v>558922.2</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1337,28 +1346,28 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I23" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>237833.89</v>
+        <v>109890.41</v>
       </c>
       <c r="L23">
-        <v>237833.89</v>
+        <v>219780.82</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1369,28 +1378,28 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J24">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>297747.47</v>
+        <v>237833.89</v>
       </c>
       <c r="L24">
-        <v>5954949.4</v>
+        <v>237833.89</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1401,28 +1410,28 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25">
-        <v>94848.23</v>
+        <v>962132.08</v>
       </c>
       <c r="L25">
-        <v>189696.46</v>
+        <v>2886396.24</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1433,28 +1442,28 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I26" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K26">
-        <v>348949.42</v>
+        <v>297747.47</v>
       </c>
       <c r="L26">
-        <v>348949.42</v>
+        <v>5954949.4</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1468,25 +1477,25 @@
         <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I27" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27">
-        <v>150117.48</v>
+        <v>94848.23</v>
       </c>
       <c r="L27">
-        <v>150117.48</v>
+        <v>189696.46</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1497,28 +1506,28 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I28" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K28">
-        <v>3641.01</v>
+        <v>150117.48</v>
       </c>
       <c r="L28">
-        <v>18205.05</v>
+        <v>150117.48</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1529,28 +1538,28 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I29" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>20800.67</v>
+        <v>3641.01</v>
       </c>
       <c r="L29">
-        <v>41601.34</v>
+        <v>18205.05</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1561,28 +1570,28 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="I30" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J30">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K30">
-        <v>3936.75</v>
+        <v>63597.22</v>
       </c>
       <c r="L30">
-        <v>185027.25</v>
+        <v>3688638.76</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1593,28 +1602,28 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I31" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>312918.09</v>
+        <v>20800.67</v>
       </c>
       <c r="L31">
-        <v>938754.27</v>
+        <v>41601.34</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1625,28 +1634,28 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="K32">
-        <v>206249.01</v>
+        <v>3936.75</v>
       </c>
       <c r="L32">
-        <v>206249.01</v>
+        <v>185027.25</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1657,28 +1666,28 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F33" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K33">
-        <v>2444357.96</v>
+        <v>312918.09</v>
       </c>
       <c r="L33">
-        <v>2444357.96</v>
+        <v>938754.27</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1689,28 +1698,28 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F34" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="I34" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="K34">
-        <v>216538.69</v>
+        <v>206249.01</v>
       </c>
       <c r="L34">
-        <v>216538.69</v>
+        <v>206249.01</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1721,33 +1730,33 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I35" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K35">
-        <v>286676.26</v>
+        <v>1024.43</v>
       </c>
       <c r="L35">
-        <v>286676.26</v>
+        <v>15366.45</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
         <v>40</v>
@@ -1756,25 +1765,25 @@
         <v>69</v>
       </c>
       <c r="D36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F36" t="s">
         <v>69</v>
       </c>
       <c r="I36" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J36">
-        <v>792</v>
+        <v>1</v>
       </c>
       <c r="K36">
-        <v>18048.24</v>
+        <v>216538.69</v>
       </c>
       <c r="L36">
-        <v>14294206.08</v>
+        <v>216538.69</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1785,60 +1794,60 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I37" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J37">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>20614.17</v>
+        <v>286676.26</v>
       </c>
       <c r="L37">
-        <v>1236850.2</v>
+        <v>286676.26</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I38" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J38">
-        <v>13</v>
+        <v>796</v>
       </c>
       <c r="K38">
-        <v>162426.15</v>
+        <v>18048.24</v>
       </c>
       <c r="L38">
-        <v>2111539.95</v>
+        <v>14366399.04</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -1849,28 +1858,28 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F39" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I39" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K39">
-        <v>261801.89</v>
+        <v>20614.17</v>
       </c>
       <c r="L39">
-        <v>261801.89</v>
+        <v>1236850.2</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1881,28 +1890,28 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="I40" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K40">
-        <v>75557.81</v>
+        <v>162426.15</v>
       </c>
       <c r="L40">
-        <v>75557.81</v>
+        <v>2111539.95</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1913,28 +1922,28 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E41" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I41" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J41">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>122009.29</v>
+        <v>261801.89</v>
       </c>
       <c r="L41">
-        <v>2318176.51</v>
+        <v>261801.89</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -1945,60 +1954,60 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E42" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I42" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J42">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>3512.14</v>
+        <v>75557.81</v>
       </c>
       <c r="L42">
-        <v>1264370.4</v>
+        <v>75557.81</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I43" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J43">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="K43">
-        <v>12659.05</v>
+        <v>122009.29</v>
       </c>
       <c r="L43">
-        <v>4607894.2</v>
+        <v>2318176.51</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2009,28 +2018,28 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E44" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I44" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J44">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>229850.62</v>
+        <v>114045.11</v>
       </c>
       <c r="L44">
-        <v>1838804.96</v>
+        <v>114045.11</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2041,60 +2050,60 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F45" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I45" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J45">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="K45">
-        <v>663.89</v>
+        <v>3512.14</v>
       </c>
       <c r="L45">
-        <v>39833.4</v>
+        <v>1264370.4</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E46" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F46" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="I46" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>364</v>
       </c>
       <c r="K46">
-        <v>163002.7</v>
+        <v>12659.05</v>
       </c>
       <c r="L46">
-        <v>163002.7</v>
+        <v>4607894.2</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2105,28 +2114,28 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F47" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="I47" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K47">
-        <v>15384.67</v>
+        <v>229850.62</v>
       </c>
       <c r="L47">
-        <v>15384.67</v>
+        <v>1838804.96</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2137,28 +2146,28 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="K48">
-        <v>193066.84</v>
+        <v>663.89</v>
       </c>
       <c r="L48">
-        <v>386133.68</v>
+        <v>39833.4</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2169,28 +2178,28 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I49" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>26517.61</v>
+        <v>12173.17</v>
       </c>
       <c r="L49">
-        <v>132588.05</v>
+        <v>12173.17</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2201,27 +2210,123 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E50" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="F50" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="K50">
+        <v>15384.67</v>
+      </c>
+      <c r="L50">
+        <v>15384.67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" t="s">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s">
+        <v>122</v>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
+      <c r="K51">
+        <v>193066.84</v>
+      </c>
+      <c r="L51">
+        <v>386133.68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D52" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52" t="s">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s">
+        <v>122</v>
+      </c>
+      <c r="J52">
+        <v>5</v>
+      </c>
+      <c r="K52">
+        <v>26517.61</v>
+      </c>
+      <c r="L52">
+        <v>132588.05</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" t="s">
+        <v>119</v>
+      </c>
+      <c r="E53" t="s">
+        <v>121</v>
+      </c>
+      <c r="F53" t="s">
+        <v>121</v>
+      </c>
+      <c r="I53" t="s">
+        <v>122</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
         <v>39099.54</v>
       </c>
-      <c r="L50">
+      <c r="L53">
         <v>39099.54</v>
       </c>
     </row>

--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -400,13 +400,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/11/2025 08:47:22</t>
+    <t>Período: 31/12/2025 08:45:38</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 26/11/2025 08:48:32</t>
+    <t>Fecha y hora de generación: 04/12/2025 08:46:46</t>
   </si>
 </sst>
 </file>

--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="150">
   <si>
     <t>Categoría</t>
   </si>
@@ -70,6 +70,9 @@
     <t>994349</t>
   </si>
   <si>
+    <t>4300677</t>
+  </si>
+  <si>
     <t>4306314</t>
   </si>
   <si>
@@ -94,7 +97,7 @@
     <t>4302712/8398</t>
   </si>
   <si>
-    <t>9501/9471 2TOR</t>
+    <t>43146000L</t>
   </si>
   <si>
     <t>A11205Z2730-SAO</t>
@@ -121,6 +124,9 @@
     <t>127760</t>
   </si>
   <si>
+    <t>131039</t>
+  </si>
+  <si>
     <t>4302312</t>
   </si>
   <si>
@@ -154,12 +160,18 @@
     <t>4302670</t>
   </si>
   <si>
+    <t>128462/128947</t>
+  </si>
+  <si>
     <t>ES423L ELG/THK</t>
   </si>
   <si>
     <t>A7331</t>
   </si>
   <si>
+    <t>1229R1032</t>
+  </si>
+  <si>
     <t>3278W335/43067</t>
   </si>
   <si>
@@ -178,6 +190,9 @@
     <t>17515</t>
   </si>
   <si>
+    <t>4304549WAP</t>
+  </si>
+  <si>
     <t>56929/500.946</t>
   </si>
   <si>
@@ -190,6 +205,12 @@
     <t>SAP1024L</t>
   </si>
   <si>
+    <t>VCC T1000903U</t>
+  </si>
+  <si>
+    <t>05-32313-001</t>
+  </si>
+  <si>
     <t>FIRESTONE</t>
   </si>
   <si>
@@ -211,6 +232,9 @@
     <t>MERITOR</t>
   </si>
   <si>
+    <t>HENDRICKSON</t>
+  </si>
+  <si>
     <t>MAHLE</t>
   </si>
   <si>
@@ -223,6 +247,9 @@
     <t>EATON CLUTCH</t>
   </si>
   <si>
+    <t>SPICER</t>
+  </si>
+  <si>
     <t>CLEVITE</t>
   </si>
   <si>
@@ -235,6 +262,9 @@
     <t>DAYCO</t>
   </si>
   <si>
+    <t>WAP</t>
+  </si>
+  <si>
     <t>SAMPA</t>
   </si>
   <si>
@@ -244,6 +274,9 @@
     <t>SAP</t>
   </si>
   <si>
+    <t>FREIGHTLINER</t>
+  </si>
+  <si>
     <t>BOLSA SILLA CZ TODAS INTER</t>
   </si>
   <si>
@@ -256,6 +289,9 @@
     <t>ASBESTO FAN CLUTCH DRIVE MASTER 8" JGOX2</t>
   </si>
   <si>
+    <t>PIÑON TRIPLIADOR 14/16/915</t>
+  </si>
+  <si>
     <t>ACOPLE ESTRIADO BALINERA 510 MONO 16E318</t>
   </si>
   <si>
@@ -280,7 +316,7 @@
     <t>RODILLO TREN FIJO PARTE TRAS - TODAS 18</t>
   </si>
   <si>
-    <t>BOLSA TAN10.12ANx5.87CCx24.50AL+7.88D+2T</t>
+    <t>PASADOR MUELLE</t>
   </si>
   <si>
     <t>RETENEDOR 23-240 / 145</t>
@@ -307,6 +343,9 @@
     <t>FRENO EMBRAGUE 2"</t>
   </si>
   <si>
+    <t>CRUCETA ESCUALIZACION 46-170</t>
+  </si>
+  <si>
     <t>ARANDELA PLANA PIÑÓN RVSO FR/FRO TODAS</t>
   </si>
   <si>
@@ -346,6 +385,9 @@
     <t>PATA SINCRONIZADOR K-3492</t>
   </si>
   <si>
+    <t>ARANDELA SATEL ESCZ S 145-230 SQHD/SQ100</t>
+  </si>
+  <si>
     <t>CRUCETA ESCUALIZACION 46160</t>
   </si>
   <si>
@@ -364,6 +406,9 @@
     <t>CORREA PARA COLUMBIA SERIE60 12LT</t>
   </si>
   <si>
+    <t>EJE CORREDI FS6406A/FSB6406A/FS5406N 38E</t>
+  </si>
+  <si>
     <t>TEFLON SUSPENSIÓN HOJA ZETA</t>
   </si>
   <si>
@@ -376,12 +421,24 @@
     <t>CÁMARA DE FRENO DE SERVICIO TIPO 24 CON CONJUNTO DE HORQUILLA</t>
   </si>
   <si>
+    <t>SENSOR DE TEMPERATURA FREIGHTLINER CASCADIA</t>
+  </si>
+  <si>
+    <t>TAPA SUPERIOR DEPOSITO REFRIGERANTE FREIGHTLINER CASCADIA</t>
+  </si>
+  <si>
     <t>CVG</t>
   </si>
   <si>
+    <t>DANA</t>
+  </si>
+  <si>
     <t>USA</t>
   </si>
   <si>
+    <t>WAP/TRANSMISION</t>
+  </si>
+  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -400,13 +457,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/12/2025 08:45:38</t>
+    <t>Período: 31/01/2026 07:43:42</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 04/12/2025 08:46:46</t>
+    <t>Fecha y hora de generación: 08/01/2026 07:44:15</t>
   </si>
 </sst>
 </file>
@@ -820,28 +877,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -857,7 +914,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -873,12 +930,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -930,19 +987,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="F10" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="I10" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -962,19 +1019,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -994,19 +1051,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1026,19 +1083,19 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1058,28 +1115,28 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>57941.1</v>
+        <v>555067.91</v>
       </c>
       <c r="L14">
-        <v>173823.3</v>
+        <v>2775339.55</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1090,28 +1147,28 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I15" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>20866.91</v>
+        <v>57941.1</v>
       </c>
       <c r="L15">
-        <v>41733.82</v>
+        <v>173823.3</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1122,28 +1179,28 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I16" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>69586.60000000001</v>
+        <v>20866.91</v>
       </c>
       <c r="L16">
-        <v>347933</v>
+        <v>41733.82</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1154,28 +1211,28 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I17" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>177348.88</v>
+        <v>69586.60000000001</v>
       </c>
       <c r="L17">
-        <v>354697.76</v>
+        <v>347933</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1186,28 +1243,28 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I18" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>241211.27</v>
+        <v>177348.88</v>
       </c>
       <c r="L18">
-        <v>241211.27</v>
+        <v>354697.76</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1218,28 +1275,28 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>70360.37</v>
+        <v>241211.27</v>
       </c>
       <c r="L19">
-        <v>492522.59</v>
+        <v>241211.27</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1250,28 +1307,28 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I20" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J20">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>525495.8</v>
+        <v>70360.37</v>
       </c>
       <c r="L20">
-        <v>6305949.6</v>
+        <v>492522.59</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1282,28 +1339,28 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I21" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K21">
-        <v>52431.62</v>
+        <v>525495.8</v>
       </c>
       <c r="L21">
-        <v>209726.48</v>
+        <v>6305949.6</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1314,28 +1371,28 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I22" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>558922.2</v>
+        <v>52431.62</v>
       </c>
       <c r="L22">
-        <v>558922.2</v>
+        <v>209726.48</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1346,28 +1403,28 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I23" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>109890.41</v>
+        <v>56434.75</v>
       </c>
       <c r="L23">
-        <v>219780.82</v>
+        <v>169304.25</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1378,28 +1435,28 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I24" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24">
-        <v>237833.89</v>
+        <v>109890.41</v>
       </c>
       <c r="L24">
-        <v>237833.89</v>
+        <v>219780.82</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1410,28 +1467,28 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>962132.08</v>
+        <v>237833.89</v>
       </c>
       <c r="L25">
-        <v>2886396.24</v>
+        <v>237833.89</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1442,28 +1499,28 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I26" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J26">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K26">
-        <v>297747.47</v>
+        <v>962132.08</v>
       </c>
       <c r="L26">
-        <v>5954949.4</v>
+        <v>2886396.24</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1477,25 +1534,25 @@
         <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I27" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K27">
-        <v>94848.23</v>
+        <v>297747.47</v>
       </c>
       <c r="L27">
-        <v>189696.46</v>
+        <v>5954949.4</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1506,28 +1563,28 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I28" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>150117.48</v>
+        <v>94848.23</v>
       </c>
       <c r="L28">
-        <v>150117.48</v>
+        <v>189696.46</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1538,28 +1595,28 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I29" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K29">
-        <v>3641.01</v>
+        <v>150117.48</v>
       </c>
       <c r="L29">
-        <v>18205.05</v>
+        <v>150117.48</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1570,28 +1627,28 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I30" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J30">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>63597.22</v>
+        <v>3641.01</v>
       </c>
       <c r="L30">
-        <v>3688638.76</v>
+        <v>18205.05</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1602,60 +1659,60 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F31" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="I31" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="K31">
-        <v>20800.67</v>
+        <v>63597.22</v>
       </c>
       <c r="L31">
-        <v>41601.34</v>
+        <v>3688638.76</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="I32" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J32">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="K32">
-        <v>3936.75</v>
+        <v>227846.21</v>
       </c>
       <c r="L32">
-        <v>185027.25</v>
+        <v>683538.63</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1666,28 +1723,28 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I33" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>312918.09</v>
+        <v>20800.67</v>
       </c>
       <c r="L33">
-        <v>938754.27</v>
+        <v>41601.34</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1698,28 +1755,28 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E34" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F34" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I34" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="K34">
-        <v>206249.01</v>
+        <v>3936.75</v>
       </c>
       <c r="L34">
-        <v>206249.01</v>
+        <v>185027.25</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1730,28 +1787,28 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F35" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I35" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J35">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K35">
-        <v>1024.43</v>
+        <v>312918.09</v>
       </c>
       <c r="L35">
-        <v>15366.45</v>
+        <v>938754.27</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1762,28 +1819,28 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I36" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36">
-        <v>216538.69</v>
+        <v>206249.01</v>
       </c>
       <c r="L36">
-        <v>216538.69</v>
+        <v>206249.01</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1794,60 +1851,60 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E37" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="I37" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K37">
-        <v>286676.26</v>
+        <v>1024.43</v>
       </c>
       <c r="L37">
-        <v>286676.26</v>
+        <v>15366.45</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E38" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F38" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I38" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J38">
-        <v>796</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>18048.24</v>
+        <v>216538.69</v>
       </c>
       <c r="L38">
-        <v>14366399.04</v>
+        <v>216538.69</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -1858,60 +1915,60 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I39" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J39">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="K39">
-        <v>20614.17</v>
+        <v>286676.26</v>
       </c>
       <c r="L39">
-        <v>1236850.2</v>
+        <v>286676.26</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E40" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I40" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J40">
-        <v>13</v>
+        <v>796</v>
       </c>
       <c r="K40">
-        <v>162426.15</v>
+        <v>18048.24</v>
       </c>
       <c r="L40">
-        <v>2111539.95</v>
+        <v>14366399.04</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1922,28 +1979,28 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E41" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F41" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I41" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K41">
-        <v>261801.89</v>
+        <v>20614.17</v>
       </c>
       <c r="L41">
-        <v>261801.89</v>
+        <v>1236850.2</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -1957,7 +2014,7 @@
         <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E42" t="s">
         <v>71</v>
@@ -1966,16 +2023,16 @@
         <v>71</v>
       </c>
       <c r="I42" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K42">
-        <v>75557.81</v>
+        <v>162426.15</v>
       </c>
       <c r="L42">
-        <v>75557.81</v>
+        <v>2111539.95</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -1986,28 +2043,28 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D43" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E43" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F43" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I43" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J43">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K43">
-        <v>122009.29</v>
+        <v>261801.89</v>
       </c>
       <c r="L43">
-        <v>2318176.51</v>
+        <v>261801.89</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2018,28 +2075,28 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E44" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="I44" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="K44">
-        <v>114045.11</v>
+        <v>292043.52</v>
       </c>
       <c r="L44">
-        <v>114045.11</v>
+        <v>292043.52</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2050,60 +2107,60 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E45" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F45" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="I45" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J45">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>3512.14</v>
+        <v>75557.81</v>
       </c>
       <c r="L45">
-        <v>1264370.4</v>
+        <v>75557.81</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D46" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F46" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I46" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J46">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="K46">
-        <v>12659.05</v>
+        <v>122009.29</v>
       </c>
       <c r="L46">
-        <v>4607894.2</v>
+        <v>2318176.51</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2114,28 +2171,28 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D47" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E47" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F47" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I47" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J47">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="K47">
-        <v>229850.62</v>
+        <v>4152.36</v>
       </c>
       <c r="L47">
-        <v>1838804.96</v>
+        <v>236684.52</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2146,28 +2203,28 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D48" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F48" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I48" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J48">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="K48">
-        <v>663.89</v>
+        <v>114045.11</v>
       </c>
       <c r="L48">
-        <v>39833.4</v>
+        <v>114045.11</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2178,60 +2235,60 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D49" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I49" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="K49">
-        <v>12173.17</v>
+        <v>3512.14</v>
       </c>
       <c r="L49">
-        <v>12173.17</v>
+        <v>1264370.4</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D50" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I50" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>632</v>
       </c>
       <c r="K50">
-        <v>15384.67</v>
+        <v>12068.27</v>
       </c>
       <c r="L50">
-        <v>15384.67</v>
+        <v>7627146.64</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2242,28 +2299,28 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E51" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F51" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K51">
-        <v>193066.84</v>
+        <v>229850.62</v>
       </c>
       <c r="L51">
-        <v>386133.68</v>
+        <v>1838804.96</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2274,28 +2331,28 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D52" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E52" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F52" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I52" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J52">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="K52">
-        <v>26517.61</v>
+        <v>663.89</v>
       </c>
       <c r="L52">
-        <v>132588.05</v>
+        <v>39833.4</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2306,28 +2363,252 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E53" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="F53" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="I53" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J53">
         <v>1</v>
       </c>
       <c r="K53">
+        <v>12173.17</v>
+      </c>
+      <c r="L53">
+        <v>12173.17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" t="s">
+        <v>82</v>
+      </c>
+      <c r="F54" t="s">
+        <v>140</v>
+      </c>
+      <c r="I54" t="s">
+        <v>141</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>447314.89</v>
+      </c>
+      <c r="L54">
+        <v>447314.89</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" t="s">
+        <v>83</v>
+      </c>
+      <c r="F55" t="s">
+        <v>83</v>
+      </c>
+      <c r="I55" t="s">
+        <v>141</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>15384.67</v>
+      </c>
+      <c r="L55">
+        <v>15384.67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" t="s">
+        <v>132</v>
+      </c>
+      <c r="E56" t="s">
+        <v>84</v>
+      </c>
+      <c r="F56" t="s">
+        <v>84</v>
+      </c>
+      <c r="I56" t="s">
+        <v>141</v>
+      </c>
+      <c r="J56">
+        <v>2</v>
+      </c>
+      <c r="K56">
+        <v>193066.84</v>
+      </c>
+      <c r="L56">
+        <v>386133.68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" t="s">
+        <v>84</v>
+      </c>
+      <c r="D57" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57" t="s">
+        <v>84</v>
+      </c>
+      <c r="F57" t="s">
+        <v>84</v>
+      </c>
+      <c r="I57" t="s">
+        <v>141</v>
+      </c>
+      <c r="J57">
+        <v>5</v>
+      </c>
+      <c r="K57">
+        <v>26517.61</v>
+      </c>
+      <c r="L57">
+        <v>132588.05</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D58" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58" t="s">
+        <v>139</v>
+      </c>
+      <c r="F58" t="s">
+        <v>139</v>
+      </c>
+      <c r="I58" t="s">
+        <v>141</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58">
         <v>39099.54</v>
       </c>
-      <c r="L53">
+      <c r="L58">
         <v>39099.54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" t="s">
+        <v>135</v>
+      </c>
+      <c r="E59" t="s">
+        <v>86</v>
+      </c>
+      <c r="F59" t="s">
+        <v>86</v>
+      </c>
+      <c r="I59" t="s">
+        <v>141</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="K59">
+        <v>36041.84</v>
+      </c>
+      <c r="L59">
+        <v>72083.67999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" t="s">
+        <v>86</v>
+      </c>
+      <c r="F60" t="s">
+        <v>86</v>
+      </c>
+      <c r="I60" t="s">
+        <v>141</v>
+      </c>
+      <c r="J60">
+        <v>10</v>
+      </c>
+      <c r="K60">
+        <v>20138.07</v>
+      </c>
+      <c r="L60">
+        <v>201380.7</v>
       </c>
     </row>
   </sheetData>

--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -457,13 +457,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/01/2026 07:43:42</t>
+    <t>Período: 31/01/2026 07:43:41</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 08/01/2026 07:44:15</t>
+    <t>Fecha y hora de generación: 09/01/2026 07:44:13</t>
   </si>
 </sst>
 </file>

--- a/VALORIZADO FALTANTES IMPO.xlsx
+++ b/VALORIZADO FALTANTES IMPO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="145">
   <si>
     <t>Categoría</t>
   </si>
@@ -205,12 +205,6 @@
     <t>SAP1024L</t>
   </si>
   <si>
-    <t>VCC T1000903U</t>
-  </si>
-  <si>
-    <t>05-32313-001</t>
-  </si>
-  <si>
     <t>FIRESTONE</t>
   </si>
   <si>
@@ -274,9 +268,6 @@
     <t>SAP</t>
   </si>
   <si>
-    <t>FREIGHTLINER</t>
-  </si>
-  <si>
     <t>BOLSA SILLA CZ TODAS INTER</t>
   </si>
   <si>
@@ -421,12 +412,6 @@
     <t>CÁMARA DE FRENO DE SERVICIO TIPO 24 CON CONJUNTO DE HORQUILLA</t>
   </si>
   <si>
-    <t>SENSOR DE TEMPERATURA FREIGHTLINER CASCADIA</t>
-  </si>
-  <si>
-    <t>TAPA SUPERIOR DEPOSITO REFRIGERANTE FREIGHTLINER CASCADIA</t>
-  </si>
-  <si>
     <t>CVG</t>
   </si>
   <si>
@@ -457,13 +442,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/01/2026 07:43:41</t>
+    <t>Período: 31/01/2026 08:56:04</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 09/01/2026 07:44:13</t>
+    <t>Fecha y hora de generación: 19/01/2026 08:56:25</t>
   </si>
 </sst>
 </file>
@@ -877,28 +862,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -914,7 +899,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -930,12 +915,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -987,19 +972,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I10" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1019,19 +1004,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1051,19 +1036,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1083,19 +1068,19 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I13" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1115,19 +1100,19 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I14" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -1147,19 +1132,19 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I15" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J15">
         <v>3</v>
@@ -1179,19 +1164,19 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I16" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -1211,19 +1196,19 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I17" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -1243,19 +1228,19 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I18" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1275,19 +1260,19 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I19" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1307,19 +1292,19 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I20" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -1339,19 +1324,19 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J21">
         <v>12</v>
@@ -1371,19 +1356,19 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I22" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -1403,19 +1388,19 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J23">
         <v>3</v>
@@ -1435,19 +1420,19 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I24" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -1467,19 +1452,19 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I25" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1499,19 +1484,19 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I26" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J26">
         <v>3</v>
@@ -1531,19 +1516,19 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I27" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J27">
         <v>20</v>
@@ -1563,19 +1548,19 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I28" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -1595,19 +1580,19 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1627,19 +1612,19 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I30" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J30">
         <v>5</v>
@@ -1659,19 +1644,19 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I31" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J31">
         <v>58</v>
@@ -1691,19 +1676,19 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E32" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F32" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I32" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -1723,19 +1708,19 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I33" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -1755,19 +1740,19 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I34" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J34">
         <v>47</v>
@@ -1787,19 +1772,19 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I35" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J35">
         <v>3</v>
@@ -1819,19 +1804,19 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I36" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -1851,19 +1836,19 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I37" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J37">
         <v>15</v>
@@ -1883,19 +1868,19 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I38" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -1915,19 +1900,19 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D39" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I39" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -1947,19 +1932,19 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I40" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J40">
         <v>796</v>
@@ -1979,19 +1964,19 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E41" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F41" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I41" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J41">
         <v>60</v>
@@ -2011,19 +1996,19 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I42" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J42">
         <v>13</v>
@@ -2043,19 +2028,19 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D43" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I43" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2075,19 +2060,19 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D44" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I44" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2107,19 +2092,19 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D45" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I45" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2139,19 +2124,19 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D46" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I46" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J46">
         <v>19</v>
@@ -2171,19 +2156,19 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I47" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J47">
         <v>57</v>
@@ -2203,19 +2188,19 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D48" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E48" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F48" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I48" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2235,19 +2220,19 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D49" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E49" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F49" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I49" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J49">
         <v>360</v>
@@ -2267,19 +2252,19 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D50" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E50" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I50" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J50">
         <v>632</v>
@@ -2299,19 +2284,19 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I51" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J51">
         <v>8</v>
@@ -2331,19 +2316,19 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I52" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J52">
         <v>60</v>
@@ -2363,19 +2348,19 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D53" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E53" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I53" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2395,19 +2380,19 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D54" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E54" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F54" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I54" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2427,19 +2412,19 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E55" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F55" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I55" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2459,19 +2444,19 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D56" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E56" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F56" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J56">
         <v>2</v>
@@ -2491,19 +2476,19 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D57" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J57">
         <v>5</v>
@@ -2523,19 +2508,19 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D58" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" t="s">
         <v>134</v>
       </c>
-      <c r="E58" t="s">
-        <v>139</v>
-      </c>
       <c r="F58" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="I58" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -2545,70 +2530,6 @@
       </c>
       <c r="L58">
         <v>39099.54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12">
-      <c r="A59" t="s">
-        <v>13</v>
-      </c>
-      <c r="B59" t="s">
-        <v>63</v>
-      </c>
-      <c r="C59" t="s">
-        <v>86</v>
-      </c>
-      <c r="D59" t="s">
-        <v>135</v>
-      </c>
-      <c r="E59" t="s">
-        <v>86</v>
-      </c>
-      <c r="F59" t="s">
-        <v>86</v>
-      </c>
-      <c r="I59" t="s">
-        <v>141</v>
-      </c>
-      <c r="J59">
-        <v>2</v>
-      </c>
-      <c r="K59">
-        <v>36041.84</v>
-      </c>
-      <c r="L59">
-        <v>72083.67999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12">
-      <c r="A60" t="s">
-        <v>12</v>
-      </c>
-      <c r="B60" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" t="s">
-        <v>86</v>
-      </c>
-      <c r="D60" t="s">
-        <v>136</v>
-      </c>
-      <c r="E60" t="s">
-        <v>86</v>
-      </c>
-      <c r="F60" t="s">
-        <v>86</v>
-      </c>
-      <c r="I60" t="s">
-        <v>141</v>
-      </c>
-      <c r="J60">
-        <v>10</v>
-      </c>
-      <c r="K60">
-        <v>20138.07</v>
-      </c>
-      <c r="L60">
-        <v>201380.7</v>
       </c>
     </row>
   </sheetData>
